--- a/OraRegaAV/FormatFiles/CustomerFormatFile.xlsx
+++ b/OraRegaAV/FormatFiles/CustomerFormatFile.xlsx
@@ -58,18 +58,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -98,19 +90,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -410,12 +399,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
     <col min="2" max="2" width="26.7109375" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" style="2" customWidth="1"/>
     <col min="4" max="4" width="23.85546875" customWidth="1"/>
     <col min="5" max="5" width="32.42578125" customWidth="1"/>
     <col min="6" max="6" width="25.5703125" customWidth="1"/>
@@ -434,7 +423,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -464,12 +453,6 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D3" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="3">
